--- a/format-laporan/hari-minggu-2026/latihan-1.xlsx
+++ b/format-laporan/hari-minggu-2026/latihan-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSPS-2026\format-laporan\hari-minggu-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F514127A-0EE6-4333-9F88-092832775A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DC5A97-A6A1-4C4E-8757-DCCE257EC903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A93B7433-952B-4DC1-A425-7BE594AB995B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="62">
   <si>
     <t>NO</t>
   </si>
@@ -169,13 +169,64 @@
   </si>
   <si>
     <t>96050464</t>
+  </si>
+  <si>
+    <t>WAYANE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KECAMATAN </t>
+  </si>
+  <si>
+    <t>AIFAT UTARA</t>
+  </si>
+  <si>
+    <t>KATHOLIK</t>
+  </si>
+  <si>
+    <t>KRISTEN</t>
+  </si>
+  <si>
+    <t>MARTAFINA SASIOR</t>
+  </si>
+  <si>
+    <t>PETA KORAIN</t>
+  </si>
+  <si>
+    <t>HERMINA YUMTE</t>
+  </si>
+  <si>
+    <t>MARTHA BARU</t>
+  </si>
+  <si>
+    <t>MATHELDA TAA</t>
+  </si>
+  <si>
+    <t>OMOS NAUW</t>
+  </si>
+  <si>
+    <t>PAULINA BAME</t>
+  </si>
+  <si>
+    <t>YOHANA KORAIN</t>
+  </si>
+  <si>
+    <t>KAWIN</t>
+  </si>
+  <si>
+    <t>BELUM KAWIN</t>
+  </si>
+  <si>
+    <t>PETANI</t>
+  </si>
+  <si>
+    <t>BELUM BEKERJA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,13 +235,32 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -220,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -237,6 +307,18 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEBF532-7042-459F-8777-22EBC446912F}">
-  <dimension ref="A2:P11"/>
+  <dimension ref="A2:Q11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.7265625" customWidth="1"/>
@@ -559,13 +641,13 @@
     <col min="3" max="3" width="21.1796875" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="10" width="17.6328125" customWidth="1"/>
-    <col min="11" max="11" width="19.54296875" customWidth="1"/>
-    <col min="12" max="12" width="21.54296875" customWidth="1"/>
-    <col min="13" max="16" width="17.6328125" customWidth="1"/>
+    <col min="6" max="11" width="17.6328125" customWidth="1"/>
+    <col min="12" max="12" width="19.54296875" customWidth="1"/>
+    <col min="13" max="13" width="21.54296875" customWidth="1"/>
+    <col min="14" max="17" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -594,24 +676,27 @@
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="1"/>
       <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -627,21 +712,36 @@
       <c r="E3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="13" t="s">
+        <v>29</v>
+      </c>
       <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="4">
         <v>23478</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="I3" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N3" s="3"/>
+      <c r="O3" s="12" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -657,21 +757,36 @@
       <c r="E4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="13" t="s">
+        <v>30</v>
+      </c>
       <c r="G4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="4">
         <v>21002</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="I4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N4" s="3"/>
+      <c r="O4" s="12" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -687,21 +802,36 @@
       <c r="E5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="13" t="s">
+        <v>31</v>
+      </c>
       <c r="G5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="4">
         <v>23548</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="I5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N5" s="3"/>
+      <c r="O5" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -717,21 +847,36 @@
       <c r="E6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="13" t="s">
+        <v>32</v>
+      </c>
       <c r="G6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H6" s="4">
         <v>35903</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="I6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N6" s="3"/>
+      <c r="O6" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -747,21 +892,36 @@
       <c r="E7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="4">
         <v>30349</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="I7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N7" s="3"/>
+      <c r="O7" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -777,21 +937,36 @@
       <c r="E8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="13" t="s">
+        <v>34</v>
+      </c>
       <c r="G8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="H8" s="4">
         <v>31124</v>
       </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="I8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N8" s="3"/>
+      <c r="O8" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -807,21 +982,36 @@
       <c r="E9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="4">
         <v>30727</v>
       </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="I9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N9" s="3"/>
+      <c r="O9" s="12" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -837,21 +1027,36 @@
       <c r="E10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="13" t="s">
+        <v>36</v>
+      </c>
       <c r="G10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H10" s="4">
         <v>29137</v>
       </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="I10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N10" s="3"/>
+      <c r="O10" s="12" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
     </row>
